--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/3_需重新出题/4轮_制造业通用_机械工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/3_需重新出题/4轮_制造业通用_机械工程师_需要重新出题.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,21 +489,9 @@
           <t>请简述机械零件刚度不足时，最直接表现出来的物理现象是什么？</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>最直接表现出来的物理现象是零件在载荷作用下发生过量弹性变形，且卸载后能完全恢复原状——也就是看得见、摸得着的‘晃动’‘偏移’‘下沉’或‘弯曲’，比如轴类件转动时跳动变大、支架受力后明显倾斜、导轨滑台定位漂移、联接法兰面出现可测间隙等。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>在制造业现场，工程师常用三类手段应对：一是结构优化，比如加筋、改截面、缩短悬臂长度，优点是不增加工序、成本低，但受限于空间和装配接口；二是材料升级，如用高弹性模量铸铁替代普通碳钢，但需同步复核铸造工艺适应性和热处理窗口，容易引发缩松或变形超差；三是支撑强化，比如增加辅助支点或改固定方式为两端支撑，实施快、验证周期短，但可能影响维修可达性或干涉周边部件。综合来看，结构优化是首选方案，因为它直接针对刚度本质——几何构型，不引入新材料兼容性风险，也无需改动产线工装。</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：加工过程中检测发现同一批零件刚度离散度突然增大。具体情况：三坐标抽检同一型号机座的安装面法向变形量标准差超限，但尺寸公差全合格。解决思路：立即核查铸造过程的型砂紧实度波动与浇注温度稳定性，重点排查模具分型面密封状态和冷却节奏是否异常，避免将问题误判为机加工误差。1个复杂问题概要：整机装配后动态刚度不足，但单件测试刚度达标。具体问题：减速箱壳体单件刚度合格，装入整机并加载运行后，轴承座区域振动传递超标，定位精度失稳。解决思路：检查壳体与基座之间的螺栓预紧力分布均匀性及垫片压缩一致性，同步评估结合面微观轮廓对接触刚度的影响，必要时采用分步拧紧+扭矩-转角双控工艺，并在关键接触区增加局部刚性补偿结构。</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>机械设计基础</t>
@@ -545,24 +533,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>某精密减速器输出轴与壳体轴承孔需保证长期运转下的同心稳定，设计图中在轴承孔上标注了以输出轴轴线为基准的同轴度公差，而实际检测时发现：各截面圆跳动均合格，但整轴旋转时轴承温升异常且寿命显著缩短。请简述该现象反映出的几何误差本质差异，并说明为何仅控制圆跳动不足以保障此工况下的配合稳定性。</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>圆跳动控制的是单个横截面轮廓相对于基准轴线的径向偏移，反映的是局部、瞬时的旋转偏差；同轴度控制的是整个被测轴线（即轴承孔中心线）相对于基准轴线（输出轴理论轴线）的整体空间位置一致性。两者约束对象不同：圆跳动管‘点’或‘段’的跳变，同轴度管‘线’的走向和位置。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>工程中常见三种方案：一是按图纸严格执行同轴度检测，用三坐标测量机沿孔全长采集多截面中心点拟合轴线，精度高但耗时长；二是改标圆柱度+位置度组合，兼顾形状与定位，检测效率提升但需重新验证装配刚度影响；三是采用功能检具模拟装配状态检测，如带基准轴芯棒+千分表扫掠，时效性好且贴近实际工况，但检具需随批次校准。综合来看，功能检具法最适配批量生产场景，在保证检测时效前提下，能暴露轴线弯曲、倾斜等同轴度失效模式，是当前产线主流选择。</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：检测合格但运行失效。具体情况：圆跳动合格仅说明各截面圆心未大幅偏移，但轴承孔轴线可能存在整体倾斜或弯曲，导致轴承内外圈在旋转中产生交变偏载，引发滚子边缘接触、润滑膜破裂。解决思路：回归装配体级验证，用激光跟踪仪或高精度芯棒+电子水平仪复测孔轴线全段方向偏差，并结合轴承预紧力实测数据反推同轴度容差边界。1个复杂问题概要：同轴度公差与轴承游隙、壳体刚度耦合失配。具体问题：铸铁壳体在螺栓预紧和热变形下发生微变形，使原本合格的同轴度在装机后劣化。解决思路：在工艺文件中明确壳体精镗工序必须在模拟装配压紧状态下进行，并将轴承座周边支撑刚度纳入GD&amp;T标注的基准体系，而非仅依赖自由状态检测结果。</t>
-        </is>
-      </c>
+          <t>某精密夹具的定位销图纸中，销体外圆标注了直径公差φ12±0.005，同时在技术要求栏注明‘定位销与导向套配合间隙须控制在0.008～0.015mm之间’；而导向套内孔图纸未标注公差，仅在技术要求中写明‘内孔按H7制造’。若实测导向套内孔为φ12.018，定位销外径为φ12.004，此时虽单个尺寸均符合各自图样要求，但装配后出现卡滞。请从图面信息一致性角度，分析该问题根源，并说明机械工程师在设计协同阶段应如何提前规避此类矛盾。</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>工程图与公差</t>
@@ -570,12 +546,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>形位公差应用</t>
+          <t>工程图表达</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>同轴度与圆跳动差异</t>
+          <t>技术要求与图面信息一致性</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -604,24 +580,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>某精密夹具的定位销图纸中，销体外圆标注了直径公差φ12±0.005，同时在技术要求栏注明‘定位销与导向套配合间隙须控制在0.008～0.015mm之间’；而导向套内孔图纸未标注公差，仅在技术要求中写明‘内孔按H7制造’。若实测导向套内孔为φ12.018，定位销外径为φ12.004，此时虽单个尺寸均符合各自图样要求，但装配后出现卡滞。请从图面信息一致性角度，分析该问题根源，并说明机械工程师在设计协同阶段应如何提前规避此类矛盾。</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>问题根源在于图面信息不一致：定位销外圆采用对称公差（φ12±0.005），即实际尺寸范围是φ11.995～φ12.005；导向套内孔按H7制造，查GB/T 1800.2—2022，φ12 H7的标准公差带是φ12.000～φ12.018；两者组合后，最小间隙可能低至φ12.000－φ12.005＝－0.005mm（即过盈），最大间隙为φ12.018－φ11.995＝0.023mm。而技术要求明确限定间隙必须为0.008～0.015mm，但图面未通过公差标注或基准引用实现该功能要求的闭环约束，导致尺寸合格却功能失效。</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>常见协同方案有四种：一是将定位销改为基轴制配合，外圆标h6，导向套内孔标H7，直接匹配标准间隙配合；二是统一在两零件图中引用同一配合代号，如‘Φ12H7/g6’并注明‘配对加工’；三是对导向套内孔补充公差标注，将其限制在φ12.008～φ12.015，与销体公差形成闭环；四是增设装配验证要求，如‘装配后用0.008mm塞尺可插入、0.015mm塞尺不可插入’。其中第三种最优——它不改变制造习惯，无需额外工艺控制，且能被检验员直接执行，兼顾设计意图传达、制造可行性与检测可操作性。</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：技术要求与尺寸公差脱节。具体情况：设计人员在技术要求中写入功能指标（如间隙范围），但未反向约束相关尺寸公差带位置或宽度，导致图面存在逻辑断点。解决思路：机械工程师应在图纸校审环节强制执行‘每项技术要求必须有对应尺寸或几何公差支撑’的检查清单。1个复杂问题概要：多零件协同公差链隐性冲突。具体问题：夹具中定位销、导向套、安装座三者共用同一基准，但各自图纸公差基准未统一，造成累积偏差超出间隙容限。解决思路：在结构设计初期启动公差分析会议，由机械工程师牵头明确装配功能尺寸链，指定主基准面，并在所有关联图纸上同步标注同一基准体系和公差框格引用。</t>
-        </is>
-      </c>
+          <t>请简述：如果某零件的工程图已升版但BOM未更新，可能带来哪些最直接的生产执行风险？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>工程图与公差</t>
@@ -629,17 +593,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>工程图表达</t>
+          <t>设计变更表达</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>技术要求与图面信息一致性</t>
+          <t>图纸版本与BOM一致性</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,42 +627,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>某泵体铸件图纸中，主视图标注了Φ80H7孔的尺寸与公差，侧视图上该孔对应位置却以‘Φ80’无公差形式表达，且技术要求栏注明‘未注公差按GB/T 1800.2—2020中IT12执行’。若实测孔径为Φ80.15，符合IT12（±0.22）但超出H7（+0.021/0）范围，该尺寸是否合格？请从图面视图间信息冲突时的优先级规则和标准条款适用逻辑说明判断依据。</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>该尺寸不合格。工程图中，同一要素在不同视图上出现尺寸标注冲突时，以明确标注公差的视图为优先；主视图已给出Φ80H7，属于有公差的正式尺寸，其要求直接覆盖侧视图的无公差简化表达；技术要求中‘未注公差按IT12执行’仅适用于图中完全未标注公差的尺寸，不适用于已有H7标注的同一要素。</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>实际工作中常用三种处理方式：一是以主视图H7为准，直接拒收超差件，响应快、责任清晰，但可能造成批量返工；二是组织设计、工艺、质量三方会签确认是否可放宽，兼顾技术严谨性与生产连续性，但耗时较长；三是核查原始设计意图，比如调阅数模或设计变更单，确认侧视图省略公差是否属制图疏漏，这是最根本的解决路径。综合来看，第三种方式最优——既守住图纸作为制造依据的法律效力，又避免将制图表达问题误判为加工质量问题。</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：设计人员在多视图中对同一尺寸采用不一致标注，且未加注说明。具体情况：侧视图省略公差是常见绘图习惯，但未同步删除或屏蔽该处尺寸，导致现场误读。解决思路：严格执行企业《机械制图审核清单》，要求所有投图前必须进行‘同要素跨视图公差一致性’专项检查。1个复杂问题概要：H7孔实际用于装配动密封，但检测时仅按尺寸判定合格，忽略形位公差与表面粗糙度联动影响。具体问题：Φ80.15虽超H7上限，但若圆度、圆柱度良好且表面无毛刺，可能仍满足泵体低压工况下的密封功能。解决思路：启动基于功能需求的‘尺寸-形位-表面’协同放行评估，由机械工程师牵头，联合密封设计与工艺人员共同签署临时使用意见，并同步推动图纸升版。</t>
-        </is>
-      </c>
+          <t>请简述焊缝符号中基本符号‘○’代表哪一种典型焊缝类型？</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>工程图与公差</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>工程图表达</t>
+          <t>焊接工艺</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>技术要求与图面信息一致性</t>
+          <t>焊缝符号表达</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -722,37 +674,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>请简述：如果某零件的工程图已升版但BOM未更新，可能带来哪些最直接的生产执行风险？</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>最直接的风险是现场作业依据与实物构型不一致：操作人员按旧BOM领料、备料或装配，而实际加工或采购需遵循新图纸要求的尺寸、公差、材料或表面处理；导致零件无法装入整机、干涉或功能失效，且问题往往在装配或终检环节才暴露。</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>常见应对方式有三种：一是人工比对图纸修订栏与BOM版本号，优点是无需系统改造，但依赖工程师责任心和时效性，易漏检；二是通过PLM系统设置图纸升版自动触发BOM校验任务，能强制闭环，但需跨部门流程协同，上线周期长；三是采用轻量级BOM冻结机制——图纸升版时锁定对应BOM条目并弹窗提醒变更责任人，兼顾响应速度与执行刚性。综合来看，第三种方式在中小批量制造场景下落地性强、容错率高，既避免系统改造成本，又防止因流程滞后造成版本脱节。</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：BOM中材料牌号未同步更新，但图纸已将45钢改为20CrMnTi。具体情况是热处理工艺参数仍按原牌号设定，导致渗碳层深度不足，零件早期磨损。解决思路是建立材料-热处理工艺映射校验规则，在BOM变更审批节点自动比对图纸材料栏与热处理工序卡要求，不匹配则阻断放行。1个复杂问题概要：图纸公差收紧（如孔径公差由±0.1改为±0.05），但BOM未更新，导致旧库存件仍在流水线使用。具体问题是该尺寸偏差引发轴系跳动超差，整机振动超标。解决思路是将关键尺寸公差带变化纳入BOM变更影响评估项，联动工艺和质量部门开展装配合规性快速验证，确认旧件是否可限用或降级使用，而非简单停用。</t>
-        </is>
-      </c>
+          <t>请简述焊缝符号中基本符号‘⊥’表示哪种常见的接头形式？</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>工程图与公差</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>设计变更表达</t>
+          <t>焊接工艺</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>图纸版本与BOM一致性</t>
+          <t>焊缝符号表达</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -781,24 +721,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>请简述焊缝符号中基本符号‘○’代表哪一种典型焊缝类型？</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>焊缝符号中的基本符号‘○’代表塞焊缝，这是一种在被焊件上预先加工出圆形通孔后，通过填充熔融金属将两板件连接起来的焊缝形式。</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>在机械结构装配中，塞焊缝主要应用于薄板叠接、加强板固定或无法实施连续角焊缝的受限空间。常见实现方式有三种：一是手工电弧焊塞焊，设备通用但熔深控制难、效率低；二是CO2气体保护半自动塞焊，熔透稳定性好、适合批量件，但对孔径公差和装配间隙敏感；三是激光填丝塞焊，热影响区小、变形低，但设备成本高、对孔位精度要求严苛。综合考虑制造节拍、设备普及度与结构可靠性，CO2气体保护半自动塞焊是当前产线最常用且工程落地性最强的方案，它能在保证单点抗剪强度的前提下，兼顾操作可重复性和现场工艺容错能力。</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：塞焊孔未焊透。具体情况：因装配间隙过大或焊接电流偏低，导致熔深不足，焊缝根部未与下层板形成冶金结合，实际承载能力大幅下降。解决思路：现场优先核查孔径与板厚匹配关系（通常孔径宜为板厚1.5～2倍），同步用焊缝量规抽检断面，确认熔深达标后，再调整电流电压参数并做工艺验证试片。1个复杂问题概要：塞焊缝用于动载荷连接时出现疲劳开裂。具体问题：在振动或交变载荷工况下，焊缝边缘应力集中叠加孔壁微裂纹，引发早期疲劳失效。解决思路：从结构层面优化，如将单点塞焊改为多点阵列分布以分散应力，同时要求焊缝边缘修磨圆滑，并在工艺文件中明确标注‘不允许存在咬边或未熔合缺陷’，配套增加磁粉检测抽检比例。</t>
-        </is>
-      </c>
+          <t>在机械加工现场，图纸上一个焊缝符号的基准线没有虚线，实心箭头指向接头一侧，且基准线上方标注‘3’、下方标注‘6’。请简述这个符号所表示的焊缝类型、两侧焊脚尺寸要求及施焊时应关注的结构对称性问题。</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -816,7 +744,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -840,24 +768,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>请简述焊缝符号中基本符号‘⊥’表示哪种常见的接头形式？</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>焊缝符号中的基本符号‘⊥’表示角接接头，也就是两块金属板以近似直角相交、在交角处形成焊缝的连接形式。这是焊接结构中最基础也最常用的接头类型之一，常见于支架、法兰加强板、箱体骨架等机械结构件的装配连接。</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>在机械工程师日常工作中，角接接头的实现主要有四种典型方案：一是单边角焊缝，适用于轻载或非关键受力部位，施工快但抗扭刚度弱；二是双边对称角焊缝，承载均衡、抗弯抗扭性能好，是绝大多数机架和底座结构的首选；三是带坡口的角焊缝，用于厚板或动载场合，熔深更大、强度更高，但需额外开坡口工序，增加工时和成本；四是T型熔透角焊缝，要求根部完全熔合，多用于高刚度需求的主承力节点，但对焊工技能和过程控制要求严格。综合考虑结构可靠性、制造效率和现场可检性，双边对称角焊缝是机械工程师在图纸设计和工艺协调中最常优先选用的方案。</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊脚尺寸实际成型偏小。具体情况：现场焊接后检测发现角焊缝焊脚高度未达图样标注值，尤其在立焊或仰焊位置，导致有效承载截面积不足，影响接头静强度与疲劳寿命。解决思路：从工艺源头核查焊丝直径、电流电压匹配及焊枪角度，同步检查装配间隙是否过大或定位焊点过少造成熔池下坠；必要时在工艺文件中明确限定最小焊脚公差并增加首件三坐标焊缝轮廓扫描验证。1个复杂问题概要：角接接头在振动工况下出现焊趾裂纹。具体问题：设备运行中焊缝起始/终止位置反复应力集中，引发微观裂纹扩展。解决思路：优化焊缝起收弧位置避开高应力区，采用退火处理消除残余应力，同时在结构设计阶段将角接改为带圆弧过渡的斜接形式，降低应力集中系数，并在维护规程中加入焊趾区域定期磁粉检测要求。</t>
-        </is>
-      </c>
+          <t>审查一份压力容器部件图纸时，看到焊缝符号基准线上方标注‘BW’、下方标注‘8’，且无虚线和箭头折线。请简单说说‘BW’代表的焊接方法类别，该标注对焊缝成型位置和坡口加工方式提出了什么基本要求。</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -875,7 +791,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -899,24 +815,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>某大型钢结构桥梁的腹板与横隔板连接处图纸标注焊缝符号：基本符号为直角三角形，引上线标注'8'，引下线标注'60°'，基准线尾部带实心箭头指向焊缝侧，且在基准线旁附加一个圆圈符号。请简述该符号组合所要求的焊接形式、对应接头的实际坡口加工方式，以及在野外风速超三级环境下实施时必须调整的两项核心工艺参数及其调整逻辑。</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>该符号表示单边V型坡口角焊缝，焊脚尺寸8毫米，坡口角度60度，实心箭头指向腹板侧，说明焊缝施焊位置在腹板一侧；圆圈符号表示全周连续焊，即该腹板与横隔板T型接头需沿整个交界长度连续施焊，不允许中断。</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>针对该T型接头，在满足桥梁结构刚度和抗疲劳要求前提下，常见方案有三种：一是采用碳钢药芯焊丝CO2气体保护焊，熔敷效率高、适应野外移动作业，但风速超三级时气流扰动大，保护效果下降；二是改用自保护药芯焊丝，无需外供保护气，抗风性好，但焊缝成形略粗、飞溅稍多，后续打磨工作量增加；三是选用低氢型手工电弧焊，工艺成熟、抗风稳定，但效率低、对焊工技能依赖强。综合时效性、质量一致性与现场可实施性，优先选用自保护药芯焊丝方案，它在保证焊缝致密性和低温韧性的同时，能有效应对野外三级以上风速带来的保护气偏吹风险。</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊缝根部未熔合。具体情况：因横隔板厚度通常大于腹板，坡口加工后装配间隙控制不严或引弧位置未充分预热，导致60度V型坡口根部金属未完全熔化。解决思路：在正式施焊前增加定位焊点预热至100℃以上，并采用小摆幅、短弧长的运条方式，确保电弧始终覆盖坡口根部区域。1个复杂问题概要：野外多变温湿度下焊缝氢致裂纹风险上升。具体问题：夜间降温快、空气湿度大，配合自保护焊丝中微量扩散氢析出，易在腹板厚板区域诱发冷裂纹。解决思路：将焊材按规范烘烤后放入保温桶随用随取，同时将层间温度控制在120～150℃区间，并在焊后2小时内完成无损检测初步扫查，确认无异常后再安排后续工序。</t>
-        </is>
-      </c>
+          <t>某输送机支架图纸中，角焊缝符号的基准线带虚线，虚线侧标注‘5’，实线侧无数字，箭头指向T型接头的立板。请简述该符号表明焊缝实际施焊在哪一侧，以及为何虚线侧的尺寸值直接决定了受力焊脚的有效高度。</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -934,7 +838,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -958,24 +862,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>一张重型机械底座装配图中，立筋与底板交接处焊缝符号由直角三角形基本符号、引上线'10'、引下线'50'及基准线右侧的'CR'辅助符号组成，同时基准线上方标注'U'。请简述该符号完整定义的焊缝类型与熔深控制目标，并说明在厚板（t≥40mm）预热后施焊过程中，如何依据此符号信息动态校验焊枪摆幅与层间温度匹配性。</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>该焊缝符号表示单边U形坡口对接焊缝，坡口深度10毫米，根部间隙50毫米，'CR'代表焊缝需完全熔透并进行背面清根处理，'U'指明坡口形状为U形。熔深控制目标是确保焊缝金属完全穿透整个板厚，形成连续无缺陷的全熔透焊缝，以满足重型机械底座在交变载荷和高刚度约束下的结构完整性要求。</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>在厚板预热施焊中，有三种常用校验方式：一是通过焊枪横向摆幅控制熔池覆盖宽度，摆幅过小易导致侧壁未熔合，过大则稀释母材、降低熔深稳定性；二是依据层间温度实测值动态调整摆幅节奏，温度偏高时适当收窄摆幅并加快行进速度，避免过热区扩大；三是结合焊道成形观察，若焊趾与母材过渡突兀或出现咬边，说明摆幅与当前层间温度不匹配。综合来看，第二种方法最可靠——它把工艺参数、热状态与结构响应联动起来，在保证焊接效率的同时，兼顾了厚板热应力分布和后续机加工余量的均匀性。</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊缝根部出现间断性未熔合。具体情况：清根后目视检查发现局部区域未露出金属光泽，或超声检测显示根部反射信号紊乱。解决思路：立即暂停焊接，复核预热温度是否在80℃～120℃区间、清根深度是否达到5毫米以上、以及焊枪在引下线对应位置是否因摆幅偏移而未能覆盖根部50毫米间隙全宽。1个复杂问题概要：多层焊过程中层间温度持续高于上限但熔深仍不足。具体问题：预热及层间测温均合格，但射线检测发现熔深波动大，部分区域仅达板厚的85%。解决思路：排查U形坡口底部曲率半径是否因机加工偏差导致电弧驻留时间不足，同步检查焊丝干伸长是否随层高增加而增大，进而削弱电弧挺度——此时需微调焊枪倾角并固定送丝导管长度，而非单纯降电流。</t>
-        </is>
-      </c>
+          <t>一张钢结构连接件图纸中，焊缝符号基准线上方标注‘C’、下方标注‘10’，且基准线末端带圆形封闭标记。请简单说说‘C’在此处代表的接头形式含义，该标注对装配间隙控制和焊接顺序安排提出了什么基础性工艺约束。</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -993,7 +885,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1017,24 +909,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>一台高振动工况下的减速机箱体图纸中，轴承座加强板与壳体连接焊缝符号含基本符号（直角三角形）、引上线'6'、引下线'45°'、基准线尾部空心箭头，且在引上线旁标注'SE'，基准线下方标注'ISO 5817-C'。请简述该符号对焊缝成形质量的关键限制项、对应焊后应力释放的必要措施，以及在批量生产中如何通过该符号信息反推夹具定位公差的上限值。</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>该焊缝符号表示单边直角角焊缝，焊脚尺寸6毫米，焊缝方向与基准面成45度倾斜，采用单面全熔透焊接方式（SE代表Single Edge，即单边开坡口全熔透），质量等级执行ISO 5817标准中的C级。关键限制项是：焊缝根部必须完全熔合、无未焊透，余高控制在0至3毫米之间，表面不得有裂纹、咬边或密集气孔；焊后必须安排去应力退火或振动时效处理；夹具定位需确保两零件装配间隙≤1.5毫米、角度偏差≤2度，否则无法稳定达成SE全熔透成形。</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>针对该SE全熔透角焊缝，常见工艺方案有三种：一是V型坡口+埋弧焊，效率高但需双面清根，返修率高；二是单面U型坡口+熔化极气体保护焊配陶瓷衬垫，一次成形好、变形小，但对装配间隙敏感；三是激光-MIG复合焊，热输入低、残余应力小，但设备成本高、编程调试周期长。综合量产稳定性、设备普及度和高振动工况可靠性，推荐U型坡口配陶瓷衬垫的MIG方案——它能在保证根部熔透前提下，将角变形控制在0.5毫米以内，且适配中小批量柔性产线。埋弧焊虽快，但清根工序易引入微裂纹风险，不适用于轴承座这类高刚度传力节点。</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1个异常情况概要：焊缝根部出现间断性未熔透；具体情况：在45度倾斜位置，陶瓷衬垫局部贴合不良或送丝角度偏移，导致电弧未能穿透根部钝边；解决思路：在首件检验中增加斜向超声波扫查，并将衬垫压紧力、焊枪倾角纳入过程巡检项，同步要求操作工每焊300毫米做一次目视根部亮线确认。1个复杂问题概要：批量焊接后轴承座安装面整体翘曲超差；具体问题：SE焊缝单侧集中热输入引发不对称收缩，叠加箱体薄壁结构刚度不足，导致轴承孔轴线偏移；解决思路：在夹具设计阶段，依据ISO 5817-C允许的余高与熔宽比例，反算热影响区塑性变形量，将原定的两点定位改为三点可调支撑加背部随形压紧，使定位公差上限从±1.2毫米收紧至±0.8毫米，并在焊后增加以轴承孔为基准的冷矫形工序。</t>
-        </is>
-      </c>
+          <t>某大型钢结构桥梁的腹板与横隔板连接处图纸标注焊缝符号：基本符号为直角三角形，引上线标注'8'，引下线标注'60°'，基准线尾部带实心箭头指向焊缝侧，且在基准线旁附加一个圆圈符号。请简述该符号组合所要求的焊接形式、对应接头的实际坡口加工方式，以及在野外风速超三级环境下实施时必须调整的两项核心工艺参数及其调整逻辑。</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>制造工艺</t>
@@ -1072,6 +952,147 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>一张重型机械底座装配图中，立筋与底板交接处焊缝符号由直角三角形基本符号、引上线'10'、引下线'50'及基准线右侧的'CR'辅助符号组成，同时基准线上方标注'U'。请简述该符号完整定义的焊缝类型与熔深控制目标，并说明在厚板（t≥40mm）预热后施焊过程中，如何依据此符号信息动态校验焊枪摆幅与层间温度匹配性。</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>制造工艺</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>焊接工艺</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>焊缝符号表达</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>某核电设备支撑架图纸中，管与法兰环焊缝采用带双引线的焊缝符号：主基准线左侧为直角三角形，引上线'12'，引下线'3×50'；右侧附加一条平行基准线，其上标注'GTAW-2G'并带'F'标记。请简述该复合标注对焊接顺序、填充金属选择及无损检测覆盖范围提出的三重约束条件，并解释为何不能将右侧标注简单理解为‘仅打底用氩弧焊’。</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>制造工艺</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>焊接工艺</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>焊缝符号表达</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>一台高振动工况下的减速机箱体图纸中，轴承座加强板与壳体连接焊缝符号含基本符号（直角三角形）、引上线'6'、引下线'45°'、基准线尾部空心箭头，且在引上线旁标注'SE'，基准线下方标注'ISO 5817-C'。请简述该符号对焊缝成形质量的关键限制项、对应焊后应力释放的必要措施，以及在批量生产中如何通过该符号信息反推夹具定位公差的上限值。</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>制造工艺</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>焊接工艺</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>焊缝符号表达</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
